--- a/SGC-CKN/Excel/d5efb904-cc7e-4766-a029-41a7af00325b_P1-158_P1-138_D800_20-03-2026.xlsx
+++ b/SGC-CKN/Excel/d5efb904-cc7e-4766-a029-41a7af00325b_P1-158_P1-138_D800_20-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
   <si>
     <t>Dự án</t>
   </si>
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>10:25 20/03/2026</t>
+    <t>10:23 20/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -165,7 +165,7 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">08:20
+    <t xml:space="preserve">08:10
 20/03/2026</t>
   </si>
   <si>
@@ -173,6 +173,10 @@
   </si>
   <si>
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08:45
+20/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">10:23
@@ -1162,16 +1166,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-1.12</v>
+        <v>-1.2</v>
       </c>
       <c r="H11" s="5">
         <v>0.17</v>
       </c>
       <c r="I11" s="5">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="J11" s="8">
-        <v>6.72</v>
+        <v>7.2</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1194,7 +1198,7 @@
         <v>33</v>
       </c>
       <c r="F12" s="9">
-        <v>-1.12</v>
+        <v>-1.2</v>
       </c>
       <c r="G12" s="9">
         <v>-3.1</v>
@@ -1203,10 +1207,10 @@
         <v>0.33</v>
       </c>
       <c r="I12" s="9">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="J12" s="8">
-        <v>5.94</v>
+        <v>5.7</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1375,13 +1379,13 @@
         <v>-39.8</v>
       </c>
       <c r="H17" s="26">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="I17" s="26">
         <v>21.3</v>
       </c>
       <c r="J17" s="8">
-        <v>18.26</v>
+        <v>21.3</v>
       </c>
       <c r="K17" s="27" t="s">
         <v>30</v>
@@ -1398,10 +1402,10 @@
         <v>50</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" s="29">
         <v>-39.8</v>
@@ -1410,13 +1414,13 @@
         <v>-44.32</v>
       </c>
       <c r="H18" s="29">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="I18" s="29">
         <v>4.52</v>
       </c>
       <c r="J18" s="19">
-        <v>2.2</v>
+        <v>2.77</v>
       </c>
       <c r="K18" s="30" t="s">
         <v>30</v>
@@ -1424,7 +1428,7 @@
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="32"/>
@@ -1530,31 +1534,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1574,16 +1578,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-1.12</v>
+        <v>-1.2</v>
       </c>
       <c r="G2" s="5">
         <v>0.17</v>
       </c>
       <c r="H2" s="5">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="I2" s="8">
-        <v>6.72</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1600,7 +1604,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-1.12</v>
+        <v>-1.2</v>
       </c>
       <c r="F3" s="9">
         <v>-3.1</v>
@@ -1609,10 +1613,10 @@
         <v>0.33</v>
       </c>
       <c r="H3" s="9">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="I3" s="8">
-        <v>5.94</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1751,13 +1755,13 @@
         <v>-39.8</v>
       </c>
       <c r="G8" s="26">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="H8" s="26">
         <v>21.3</v>
       </c>
       <c r="I8" s="8">
-        <v>18.26</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1780,18 +1784,18 @@
         <v>-44.32</v>
       </c>
       <c r="G9" s="29">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="H9" s="29">
         <v>4.52</v>
       </c>
       <c r="I9" s="19">
-        <v>2.2</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>30</v>
@@ -1809,13 +1813,13 @@
         <v>-44.32</v>
       </c>
       <c r="G10" s="34">
-        <v>7.38</v>
+        <v>6.8</v>
       </c>
       <c r="H10" s="34">
         <v>44.32</v>
       </c>
       <c r="I10" s="34">
-        <v>6</v>
+        <v>6.52</v>
       </c>
     </row>
   </sheetData>
